--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_76_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_76_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3103</v>
+        <v>6.2329</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4514</v>
+        <v>3.7437</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8589</v>
+        <v>2.4892</v>
       </c>
       <c r="G2" t="n">
         <v>3.6918</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2576</v>
+        <v>1.1802</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4312</v>
+        <v>0.7235</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8263</v>
+        <v>0.4567</v>
       </c>
       <c r="V2" t="n">
         <v>3.2166</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7303</v>
+        <v>6.1554</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1547</v>
+        <v>3.2101</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5756</v>
+        <v>2.9452</v>
       </c>
       <c r="G3" t="n">
-        <v>8.4054</v>
+        <v>3.0508</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6876</v>
+        <v>2.7563</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7178</v>
+        <v>0.2944</v>
       </c>
       <c r="J3" t="n">
-        <v>7.226</v>
+        <v>1.6071</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4485</v>
+        <v>1.7309</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7775</v>
+        <v>-0.1239</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1794</v>
+        <v>1.4437</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2391</v>
+        <v>1.0254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9403</v>
+        <v>0.4183</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.2473</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1779</v>
+        <v>0.8727</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2636</v>
+        <v>0.7628</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0857</v>
+        <v>0.1098</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6939</v>
+        <v>5.6535</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0175</v>
+        <v>3.1114</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6764</v>
+        <v>2.542</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0508</v>
+        <v>8.4054</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7563</v>
+        <v>3.6876</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2944</v>
+        <v>4.7178</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6071</v>
+        <v>7.226</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7309</v>
+        <v>3.4485</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1239</v>
+        <v>3.7775</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4437</v>
+        <v>1.1794</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0254</v>
+        <v>0.2391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4183</v>
+        <v>0.9403</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-4.871</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4112</v>
+        <v>0.101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5702</v>
+        <v>0.2203</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.159</v>
+        <v>-0.1193</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2579</v>
+        <v>5.5446</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7123</v>
+        <v>3.0661</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5457</v>
+        <v>2.4784</v>
       </c>
       <c r="G5" t="n">
         <v>2.8967</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1748</v>
+        <v>0.1118</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1415</v>
+        <v>0.2124</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0334</v>
+        <v>-0.1006</v>
       </c>
       <c r="V5" t="n">
         <v>1.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.8724</v>
+        <v>5.1755</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8151</v>
+        <v>4.051</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0573</v>
+        <v>1.1245</v>
       </c>
       <c r="G6" t="n">
         <v>6.1759</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2855</v>
+        <v>0.0176</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0615</v>
+        <v>0.0057</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.21</v>
+        <v>4.1667</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0227</v>
+        <v>1.9794</v>
       </c>
       <c r="F7" t="n">
         <v>2.1873</v>
@@ -1000,10 +1000,10 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.051</v>
+        <v>0.0077</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1142</v>
+        <v>0.0709</v>
       </c>
       <c r="U7" t="n">
         <v>-0.0633</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9026</v>
+        <v>2.0877</v>
       </c>
       <c r="E8" t="n">
-        <v>1.064</v>
+        <v>1.1819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8386</v>
+        <v>0.9058</v>
       </c>
       <c r="G8" t="n">
         <v>2.8761</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2776</v>
+        <v>-0.0925</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8507</v>
+        <v>1.6985</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2862</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5645</v>
+        <v>1.7661</v>
       </c>
       <c r="G9" t="n">
         <v>0.4743</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5904</v>
+        <v>0.4382</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6449</v>
+        <v>0.291</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0545</v>
+        <v>0.1472</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1341</v>
+        <v>1.108</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.773</v>
+        <v>-1.6983</v>
       </c>
       <c r="F10" t="n">
-        <v>2.907</v>
+        <v>2.8062</v>
       </c>
       <c r="G10" t="n">
         <v>1.0193</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1893</v>
+        <v>-0.2155</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1142</v>
+        <v>0.1889</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3035</v>
+        <v>-0.4044</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4009</v>
+        <v>-0.174</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0565</v>
+        <v>-0.6279</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6556</v>
+        <v>0.4539</v>
       </c>
       <c r="G11" t="n">
         <v>1.6678</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8109</v>
+        <v>-0.584</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.2436</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1388</v>
+        <v>-0.3404</v>
       </c>
       <c r="V11" t="n">
         <v>-2.6495</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4702</v>
+        <v>-2.1842</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8121</v>
+        <v>-2.6942</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3419</v>
+        <v>0.51</v>
       </c>
       <c r="G12" t="n">
         <v>2.7046</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3192</v>
+        <v>-1.0332</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7218</v>
+        <v>-0.5537</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>35.0911</v>
+        <v>35.4646</v>
       </c>
       <c r="E13" t="n">
-        <v>14.8823</v>
+        <v>15.2556</v>
       </c>
       <c r="F13" t="n">
-        <v>20.2088</v>
+        <v>20.2086</v>
       </c>
       <c r="G13" t="n">
         <v>35.8872</v>
@@ -1468,13 +1468,13 @@
         <v>11.5977</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4308000000000007</v>
+        <v>0.8040000000000003</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4364</v>
+        <v>1.8098</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0061</v>
+        <v>-1.0059</v>
       </c>
       <c r="V13" t="n">
         <v>4.5723</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7846</v>
+        <v>0.7006</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6347</v>
+        <v>1.6645</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1499</v>
+        <v>-0.9639</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1065</v>
+        <v>0.3043</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8054</v>
+        <v>1.1776</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3011</v>
+        <v>-0.8733</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5373</v>
+        <v>2.2736</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.2366</v>
+        <v>1.8822</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6993</v>
+        <v>0.3914</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5692</v>
+        <v>-1.9692</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5688</v>
+        <v>-0.7045</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0004</v>
+        <v>-1.2647</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0329</v>
+        <v>-1.2274</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3318</v>
+        <v>-0.6091</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7010999999999999</v>
+        <v>-0.6183</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0886</v>
+        <v>0.3022</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3106</v>
+        <v>0.8296</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.222</v>
+        <v>-0.5274</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3043</v>
+        <v>-0.6883</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1776</v>
+        <v>-2.4215</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8733</v>
+        <v>1.7332</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2736</v>
+        <v>1.9535</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8822</v>
+        <v>-0.9909</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3914</v>
+        <v>2.9444</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9692</v>
+        <v>-2.6418</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7045</v>
+        <v>-1.4306</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2647</v>
+        <v>-1.2112</v>
       </c>
       <c r="P15" t="n">
         <v>1.6237</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8394</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>0.0358</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8764</v>
+        <v>-0.1329</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0492</v>
+        <v>-0.648</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4757</v>
+        <v>1.3515</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4266</v>
+        <v>-1.9995</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6883</v>
+        <v>-1.7207</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4215</v>
+        <v>-0.0444</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7332</v>
+        <v>-1.6763</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9535</v>
+        <v>0.1846</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9909</v>
+        <v>0.8605</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9444</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6418</v>
+        <v>-1.9053</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4306</v>
+        <v>-0.9049</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2112</v>
+        <v>-1.0004</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3501</v>
+        <v>-0.105</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3181</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0321</v>
+        <v>-0.1997</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-1.1356</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9412</v>
+        <v>-1.0166</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0331</v>
+        <v>-0.119</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7207</v>
+        <v>-2.1065</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0444</v>
+        <v>-1.8054</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6763</v>
+        <v>-0.3011</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1846</v>
+        <v>-0.5373</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8605</v>
+        <v>-1.2366</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.6993</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9053</v>
+        <v>-1.5692</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9049</v>
+        <v>-0.5688</v>
       </c>
       <c r="O17" t="n">
         <v>-1.0004</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4512</v>
+        <v>1.1127</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6844</v>
+        <v>0.6805</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2333</v>
+        <v>0.4323</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2995</v>
+        <v>-1.9355</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4481</v>
+        <v>0.6135</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8514</v>
+        <v>-2.549</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6282</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1505</v>
+        <v>0.2135</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7978</v>
+        <v>0.2638</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3528</v>
+        <v>-0.0503</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6083</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4212</v>
+        <v>-2.8314</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8922</v>
+        <v>-3.3024</v>
       </c>
       <c r="F19" t="n">
         <v>0.471</v>
@@ -1936,10 +1936,10 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1415</v>
+        <v>0.4483</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U19" t="n">
         <v>0.3734</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1207</v>
+        <v>-4.1479</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2799</v>
+        <v>-1.162</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8407</v>
+        <v>-2.9859</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4629</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.351</v>
+        <v>-0.3782</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.326</v>
+        <v>-0.208</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.025</v>
+        <v>-0.1702</v>
       </c>
       <c r="V20" t="n">
         <v>-2.0026</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9513</v>
+        <v>-4.6596</v>
       </c>
       <c r="E21" t="n">
         <v>-3.6559</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2954</v>
+        <v>-1.0037</v>
       </c>
       <c r="G21" t="n">
         <v>-5.8973</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.036</v>
+        <v>0.2557</v>
       </c>
       <c r="T21" t="n">
         <v>0.3462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3822</v>
+        <v>-0.0905</v>
       </c>
       <c r="V21" t="n">
         <v>1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5001</v>
+        <v>-5.6961</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6354</v>
+        <v>-2.7533</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8648</v>
+        <v>-2.9427</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2973</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5223</v>
+        <v>-0.7183</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4007</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1217</v>
+        <v>-0.1997</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3</v>
+        <v>-6.8469</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3826</v>
+        <v>-7.0975</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9174</v>
+        <v>0.2506</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3598</v>
+        <v>-9.6061</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.6844</v>
+        <v>-2.7934</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3246</v>
+        <v>-6.8127</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7296</v>
+        <v>-7.3966</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.3184</v>
+        <v>-1.2163</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5889</v>
+        <v>-6.1803</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6303</v>
+        <v>-2.2095</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.366</v>
+        <v>-1.5771</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2643</v>
+        <v>-0.6323</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.2473</v>
+        <v>1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2375</v>
+        <v>0.7207</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8442</v>
+        <v>0.2992</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6067</v>
+        <v>0.4215</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9304</v>
+        <v>0.6468</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.328900000000001</v>
+        <v>-7.4066</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.276999999999999</v>
+        <v>-5.6801</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0519</v>
+        <v>-1.7265</v>
       </c>
       <c r="G24" t="n">
-        <v>-9.6061</v>
+        <v>-3.3598</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7934</v>
+        <v>-3.6844</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.8127</v>
+        <v>0.3246</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.3966</v>
+        <v>-1.7296</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2163</v>
+        <v>-2.3184</v>
       </c>
       <c r="L24" t="n">
-        <v>-6.1803</v>
+        <v>0.5889</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2095</v>
+        <v>-1.6303</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5771</v>
+        <v>-1.366</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6323</v>
+        <v>-0.2643</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3917</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R24" t="n">
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7613</v>
+        <v>0.1309</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8804</v>
+        <v>0.5467</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1191</v>
+        <v>-0.4158</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6468</v>
+        <v>-0.9304</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6468</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-35.0911</v>
+        <v>-34.3048</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.2089</v>
+        <v>-20.2087</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.8824</v>
+        <v>-14.096</v>
       </c>
       <c r="G25" t="n">
         <v>-35.8869</v>
@@ -2383,7 +2383,7 @@
         <v>-6.214700000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-7.0443</v>
+        <v>-7.044300000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-22.6279</v>
@@ -2404,13 +2404,13 @@
         <v>17.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4304999999999998</v>
+        <v>0.3557999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0057</v>
+        <v>1.0061</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4366</v>
+        <v>-0.6501999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-4.5724</v>
